--- a/data/proyectos_fortalecidos.xlsx
+++ b/data/proyectos_fortalecidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE51"/>
+  <dimension ref="A1:AL81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +584,41 @@
           <t>Fecha_Verificacion</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Beneficiarios</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Direccion</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha_actualizacion</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Pais</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo_cooperacion</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -715,7 +750,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z2" t="b">
+      <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="inlineStr">
@@ -728,10 +763,10 @@
           <t>Araucanía</t>
         </is>
       </c>
-      <c r="AC2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="b">
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="inlineStr">
@@ -739,6 +774,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -870,7 +912,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z3" t="b">
+      <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,10 +925,10 @@
           <t>Biobío</t>
         </is>
       </c>
-      <c r="AC3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="b">
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="inlineStr">
@@ -894,6 +936,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1025,7 +1074,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z4" t="b">
+      <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1038,10 +1087,10 @@
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="AC4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="b">
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1</v>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1049,6 +1098,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1180,7 +1236,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z5" t="b">
+      <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1193,10 +1249,10 @@
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="AC5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD5" t="b">
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1</v>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1204,6 +1260,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1335,7 +1398,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z6" t="b">
+      <c r="Z6" t="n">
         <v>1</v>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,10 +1411,10 @@
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="AC6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD6" t="b">
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1</v>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1359,6 +1422,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1490,7 +1560,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z7" t="b">
+      <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1503,10 +1573,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD7" t="b">
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1514,6 +1584,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1645,7 +1722,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z8" t="b">
+      <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1658,10 +1735,10 @@
           <t>Biobío</t>
         </is>
       </c>
-      <c r="AC8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD8" t="b">
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1</v>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1669,6 +1746,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1800,7 +1884,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z9" t="b">
+      <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1813,10 +1897,10 @@
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="AC9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD9" t="b">
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1</v>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1824,6 +1908,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1955,7 +2046,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z10" t="b">
+      <c r="Z10" t="n">
         <v>1</v>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1968,10 +2059,10 @@
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="AC10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD10" t="b">
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1979,6 +2070,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2110,7 +2208,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z11" t="b">
+      <c r="Z11" t="n">
         <v>1</v>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2123,10 +2221,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD11" t="b">
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1</v>
       </c>
       <c r="AE11" t="inlineStr">
@@ -2134,6 +2232,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2265,7 +2370,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z12" t="b">
+      <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2278,10 +2383,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD12" t="b">
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="inlineStr">
@@ -2289,6 +2394,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2420,7 +2532,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z13" t="b">
+      <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2433,10 +2545,10 @@
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="AC13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD13" t="b">
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1</v>
       </c>
       <c r="AE13" t="inlineStr">
@@ -2444,6 +2556,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2575,7 +2694,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z14" t="b">
+      <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2588,10 +2707,10 @@
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="AC14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD14" t="b">
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2599,6 +2718,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2730,7 +2856,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z15" t="b">
+      <c r="Z15" t="n">
         <v>1</v>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2743,10 +2869,10 @@
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="AC15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD15" t="b">
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1</v>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2754,6 +2880,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2885,7 +3018,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z16" t="b">
+      <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2898,10 +3031,10 @@
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="AC16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD16" t="b">
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1</v>
       </c>
       <c r="AE16" t="inlineStr">
@@ -2909,6 +3042,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3040,7 +3180,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z17" t="b">
+      <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="inlineStr">
@@ -3053,10 +3193,10 @@
           <t>Biobío</t>
         </is>
       </c>
-      <c r="AC17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD17" t="b">
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1</v>
       </c>
       <c r="AE17" t="inlineStr">
@@ -3064,6 +3204,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3195,7 +3342,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z18" t="b">
+      <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3208,10 +3355,10 @@
           <t>Biobío</t>
         </is>
       </c>
-      <c r="AC18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD18" t="b">
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1</v>
       </c>
       <c r="AE18" t="inlineStr">
@@ -3219,6 +3366,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3350,7 +3504,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z19" t="b">
+      <c r="Z19" t="n">
         <v>1</v>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3363,10 +3517,10 @@
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="AC19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD19" t="b">
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1</v>
       </c>
       <c r="AE19" t="inlineStr">
@@ -3374,6 +3528,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3505,7 +3666,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z20" t="b">
+      <c r="Z20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3518,10 +3679,10 @@
           <t>Biobío</t>
         </is>
       </c>
-      <c r="AC20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD20" t="b">
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1</v>
       </c>
       <c r="AE20" t="inlineStr">
@@ -3529,6 +3690,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3660,7 +3828,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z21" t="b">
+      <c r="Z21" t="n">
         <v>1</v>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3673,10 +3841,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD21" t="b">
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1</v>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3684,6 +3852,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3815,7 +3990,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z22" t="b">
+      <c r="Z22" t="n">
         <v>1</v>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3828,10 +4003,10 @@
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="AC22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD22" t="b">
+      <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="inlineStr">
@@ -3839,6 +4014,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3970,7 +4152,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z23" t="b">
+      <c r="Z23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3983,10 +4165,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD23" t="b">
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3994,6 +4176,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4125,7 +4314,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z24" t="b">
+      <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="inlineStr">
@@ -4138,10 +4327,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD24" t="b">
+      <c r="AC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1</v>
       </c>
       <c r="AE24" t="inlineStr">
@@ -4149,6 +4338,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4280,7 +4476,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z25" t="b">
+      <c r="Z25" t="n">
         <v>1</v>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4293,10 +4489,10 @@
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="AC25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD25" t="b">
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1</v>
       </c>
       <c r="AE25" t="inlineStr">
@@ -4304,6 +4500,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4435,7 +4638,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z26" t="b">
+      <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4448,10 +4651,10 @@
           <t>Araucanía</t>
         </is>
       </c>
-      <c r="AC26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD26" t="b">
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1</v>
       </c>
       <c r="AE26" t="inlineStr">
@@ -4459,6 +4662,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4590,7 +4800,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z27" t="b">
+      <c r="Z27" t="n">
         <v>1</v>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4603,10 +4813,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD27" t="b">
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1</v>
       </c>
       <c r="AE27" t="inlineStr">
@@ -4614,6 +4824,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4745,7 +4962,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z28" t="b">
+      <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4758,10 +4975,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD28" t="b">
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1</v>
       </c>
       <c r="AE28" t="inlineStr">
@@ -4769,6 +4986,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4900,7 +5124,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z29" t="b">
+      <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4913,10 +5137,10 @@
           <t>Biobío</t>
         </is>
       </c>
-      <c r="AC29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD29" t="b">
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1</v>
       </c>
       <c r="AE29" t="inlineStr">
@@ -4924,6 +5148,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5055,7 +5286,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z30" t="b">
+      <c r="Z30" t="n">
         <v>1</v>
       </c>
       <c r="AA30" t="inlineStr">
@@ -5068,10 +5299,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD30" t="b">
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="inlineStr">
@@ -5079,6 +5310,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5210,7 +5448,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z31" t="b">
+      <c r="Z31" t="n">
         <v>1</v>
       </c>
       <c r="AA31" t="inlineStr">
@@ -5223,10 +5461,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD31" t="b">
+      <c r="AC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1</v>
       </c>
       <c r="AE31" t="inlineStr">
@@ -5234,6 +5472,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5365,7 +5610,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z32" t="b">
+      <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5378,10 +5623,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD32" t="b">
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1</v>
       </c>
       <c r="AE32" t="inlineStr">
@@ -5389,6 +5634,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5520,7 +5772,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z33" t="b">
+      <c r="Z33" t="n">
         <v>1</v>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5533,10 +5785,10 @@
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="AC33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD33" t="b">
+      <c r="AC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1</v>
       </c>
       <c r="AE33" t="inlineStr">
@@ -5544,6 +5796,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5675,7 +5934,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z34" t="b">
+      <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5688,10 +5947,10 @@
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="AC34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD34" t="b">
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1</v>
       </c>
       <c r="AE34" t="inlineStr">
@@ -5699,6 +5958,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5830,7 +6096,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z35" t="b">
+      <c r="Z35" t="n">
         <v>1</v>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5843,10 +6109,10 @@
           <t>Araucanía</t>
         </is>
       </c>
-      <c r="AC35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD35" t="b">
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="n">
         <v>1</v>
       </c>
       <c r="AE35" t="inlineStr">
@@ -5854,6 +6120,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5985,7 +6258,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z36" t="b">
+      <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5998,10 +6271,10 @@
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="AC36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD36" t="b">
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
         <v>1</v>
       </c>
       <c r="AE36" t="inlineStr">
@@ -6009,6 +6282,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6140,7 +6420,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z37" t="b">
+      <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="inlineStr">
@@ -6153,10 +6433,10 @@
           <t>Biobío</t>
         </is>
       </c>
-      <c r="AC37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD37" t="b">
+      <c r="AC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1</v>
       </c>
       <c r="AE37" t="inlineStr">
@@ -6164,6 +6444,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6295,7 +6582,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z38" t="b">
+      <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6308,10 +6595,10 @@
           <t>Araucanía</t>
         </is>
       </c>
-      <c r="AC38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD38" t="b">
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1</v>
       </c>
       <c r="AE38" t="inlineStr">
@@ -6319,6 +6606,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6450,7 +6744,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z39" t="b">
+      <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6463,10 +6757,10 @@
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="AC39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD39" t="b">
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1</v>
       </c>
       <c r="AE39" t="inlineStr">
@@ -6474,6 +6768,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6605,7 +6906,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z40" t="b">
+      <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6618,10 +6919,10 @@
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="AC40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD40" t="b">
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1</v>
       </c>
       <c r="AE40" t="inlineStr">
@@ -6629,6 +6930,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6760,7 +7068,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z41" t="b">
+      <c r="Z41" t="n">
         <v>1</v>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6773,10 +7081,10 @@
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="AC41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD41" t="b">
+      <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1</v>
       </c>
       <c r="AE41" t="inlineStr">
@@ -6784,6 +7092,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6915,7 +7230,7 @@
           <t>2025-10-20 15:54:41</t>
         </is>
       </c>
-      <c r="Z42" t="b">
+      <c r="Z42" t="n">
         <v>1</v>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6928,10 +7243,10 @@
           <t>Biobío</t>
         </is>
       </c>
-      <c r="AC42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD42" t="b">
+      <c r="AC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1</v>
       </c>
       <c r="AE42" t="inlineStr">
@@ -6939,6 +7254,13 @@
           <t>2025-10-20 15:57:10</t>
         </is>
       </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7070,7 +7392,7 @@
           <t>2025-10-20 16:16:41</t>
         </is>
       </c>
-      <c r="Z43" t="b">
+      <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="inlineStr">
@@ -7086,6 +7408,13 @@
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7217,7 +7546,7 @@
           <t>2025-10-20 16:16:41</t>
         </is>
       </c>
-      <c r="Z44" t="b">
+      <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="inlineStr">
@@ -7233,6 +7562,13 @@
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7364,7 +7700,7 @@
           <t>2025-10-20 16:16:41</t>
         </is>
       </c>
-      <c r="Z45" t="b">
+      <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7380,6 +7716,13 @@
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7511,7 +7854,7 @@
           <t>2025-10-20 16:16:41</t>
         </is>
       </c>
-      <c r="Z46" t="b">
+      <c r="Z46" t="n">
         <v>1</v>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7527,6 +7870,13 @@
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7658,7 +8008,7 @@
           <t>2025-10-20 16:16:41</t>
         </is>
       </c>
-      <c r="Z47" t="b">
+      <c r="Z47" t="n">
         <v>1</v>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7674,6 +8024,13 @@
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7805,7 +8162,7 @@
           <t>2025-10-20 16:16:41</t>
         </is>
       </c>
-      <c r="Z48" t="b">
+      <c r="Z48" t="n">
         <v>1</v>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7821,6 +8178,13 @@
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7952,7 +8316,7 @@
           <t>2025-10-20 16:16:41</t>
         </is>
       </c>
-      <c r="Z49" t="b">
+      <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7968,6 +8332,13 @@
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8099,7 +8470,7 @@
           <t>2025-10-20 16:16:41</t>
         </is>
       </c>
-      <c r="Z50" t="b">
+      <c r="Z50" t="n">
         <v>1</v>
       </c>
       <c r="AA50" t="inlineStr">
@@ -8115,6 +8486,13 @@
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8246,7 +8624,7 @@
           <t>2025-10-20 16:16:41</t>
         </is>
       </c>
-      <c r="Z51" t="b">
+      <c r="Z51" t="n">
         <v>1</v>
       </c>
       <c r="AA51" t="inlineStr">
@@ -8262,6 +8640,3013 @@
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Programa de Desarrollo Rural Sostenible - FAO 2024</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FAO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Desarrollo Rural</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>USD 2,500,000</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Programa para el desarrollo rural sostenible y seguridad alimentaria en América Latina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Proyectos de desarrollo rural, seguridad alimentaria</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/procurement/current-tenders-and-calls/desarrollo-rural-sostenible</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>procurement@fao.org</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Programa Internacional</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Gobiernos, ONGs, Organizaciones</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>+39 06 57051</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Viale delle Terme di Caracalla, 00153 Roma, Italia</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Fondo de Desarrollo Rural - BID 2024</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Desarrollo Rural</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>USD 5,000,000</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Fondo para proyectos de desarrollo rural e infraestructura en zonas rurales</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Proyectos de desarrollo rural, infraestructura</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.iadb.org/es/licitaciones-y-adquisiciones/desarrollo-rural</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>procurement@iadb.org</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Fondo Internacional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Gobiernos, ONGs, Organizaciones</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>+1 202 623 1000</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>1300 New York Avenue NW, Washington, DC 20577, USA</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Programa de Innovación Agrícola - FIA 2024</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Innovación Tecnológica</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CLP 1,000,000,000</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Programa de apoyo a la innovación en el sector agrícola con tecnología de punta</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Proyectos de innovación agrícola, tecnología</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.fia.cl/convocatorias/innovacion-agricola-2024</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>innovacion@fia.cl</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Programa de Innovación</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Empresas, Centros de I+D, Universidades</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>+56 2 2431 3000</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Av. Bulnes 140, Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Fondo de Innovación Tecnológica - CORFO 2024</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CORFO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Innovación Tecnológica</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CLP 800,000,000</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fondo para proyectos de innovación tecnológica en el sector agropecuario</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Proyectos de innovación tecnológica</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://corfo.cl/sites/cpp/programasyconvocatorias/innovacion-tecnologica</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>innovacion@corfo.cl</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Fondo de Innovación</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Empresas, Startups, Centros de I+D</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>+56 2 2500 4000</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Moneda 921, Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Programa de Agricultura Sostenible - GCF 2024</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GCF</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Agricultura Sostenible</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>USD 3,000,000</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Programa para proyectos de agricultura sostenible y adaptación al cambio climático</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Proyectos de agricultura sostenible, adaptación climática</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.greenclimate.fund/funding/rfp-rfq/agricultura-sostenible</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>info@greenclimate.fund</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Fondo Climático</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Gobiernos, Organizaciones internacionales</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>+82 32 458 6000</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>175 Art Center-daero, Yeonsu-gu, Incheon 22004, República de Corea</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Fondo de Agricultura Regenerativa - Rockefeller 2024</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Rockefeller Foundation</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Agricultura Sostenible</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>USD 1,500,000</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Fondo para proyectos de agricultura regenerativa y sistemas alimentarios sostenibles</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Proyectos de agricultura regenerativa</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.rockefellerfoundation.org/our-work/agricultura-regenerativa</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>grants@rockefellerfoundation.org</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Fondo de Fundación</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Organizaciones, Empresas, Centros de investigación</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>+1 212 869 8500</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>420 Fifth Avenue, New York, NY 10018, USA</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Fundación</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Programa de Seguridad Alimentaria - PNUD 2024</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PNUD</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Seguridad Alimentaria</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>USD 2,000,000</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Programa para mejorar la seguridad alimentaria y nutrición en América Latina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Proyectos de seguridad alimentaria</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://procurement-notices.undp.org/seguridad-alimentaria</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>procurement@undp.org</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Programa Internacional</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Gobiernos, ONGs, Organizaciones</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>+1 212 906 5000</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>One United Nations Plaza, New York, NY 10017, USA</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Fondo de Nutrición - GAFSP 2024</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GAFSP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Seguridad Alimentaria</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>USD 4,000,000</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Fondo para proyectos de nutrición y seguridad alimentaria en países en desarrollo</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Proyectos de nutrición, seguridad alimentaria</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.gafspfund.org/call-proposals/nutricion</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>info@gafspfund.org</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Fondo Global</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Gobiernos, Organizaciones internacionales</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>+1 202 473 1000</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>1818 H Street NW, Washington, DC 20433, USA</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Programa de Cooperación Chile-Canadá 2024</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Embajada de Canadá</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Cooperación Internacional</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CAD 500,000</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Programa de cooperación bilateral en agricultura sostenible y cambio climático</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Proyectos de cooperación bilateral</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.canadainternational.gc.ca/chile-chili/cooperation-chile-canada</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>cooperation@international.gc.ca</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Cooperación Bilateral</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Instituciones, Universidades, Centros de investigación</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>+56 2 2204 3000</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Nueva Tajamar 481, Torre Norte, Piso 12, Las Condes, Santiago</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Bilateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Programa de Cooperación Chile-Alemania 2024</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Embajada de Alemania</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Cooperación Internacional</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EUR 300,000</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Programa de cooperación técnica en desarrollo sostenible y tecnología</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Proyectos de cooperación técnica</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://chile.diplo.de/cl-es/cooperation-chile-alemania</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>cooperation@santiago.diplo.de</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Cooperación Técnica</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Instituciones, Empresas, Centros de I+D</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>+56 2 2463 2500</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Las Hualtatas 5677, Vitacura, Santiago</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Bilateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Fondo de Desarrollo Comunitario - Kellogg 2024</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kellogg Foundation</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Desarrollo Comunitario</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>USD 200,000</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fondo para proyectos de desarrollo comunitario y equidad social</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Proyectos de desarrollo comunitario</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.wkkf.org/what-we-do/chile/desarrollo-comunitario</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>chile@wkkf.org</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Fondo de Fundación</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Organizaciones comunitarias, ONGs</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>+1 269 968 1611</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>One Michigan Avenue East, Battle Creek, MI 49017, USA</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>Fundación</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Fondo de Justicia Social - Ford 2024</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ford Foundation</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Justicia Social</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>USD 300,000</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Fondo para proyectos de justicia social y desarrollo rural equitativo</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Proyectos de justicia social</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.fordfoundation.org/work/our-grants/justicia-social</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>grants@fordfoundation.org</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>Fondo de Fundación</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Organizaciones de justicia social</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>+1 212 573 5000</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>320 E 43rd St, New York, NY 10017, USA</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Fundación</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Programa de Desarrollo Rural Integral - INDAP 2024</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>INDAP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Desarrollo Rural</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CLP 2,000,000,000</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Programa integral para el desarrollo rural y la agricultura familiar campesina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Agricultores familiares, proyectos rurales</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.indap.gob.cl/desarrollo-rural-integral</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>desarrollo@indap.gob.cl</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Programa Nacional</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Agricultores familiares, Cooperativas, Asociaciones</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>+56 2 2500 4000</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Teatinos 40, Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Programa de AgTech - CORFO 2024</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CORFO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Innovación Tecnológica</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CLP 1,500,000,000</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Programa especializado en tecnología agrícola y agricultura 4.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Proyectos de tecnología agrícola</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://corfo.cl/sites/cpp/programasyconvocatorias/agtech</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>agtech@corfo.cl</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>Programa de Innovación</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Startups AgTech, Empresas tecnológicas</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>+56 2 2500 4000</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Moneda 921, Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Programa de Agricultura Sostenible - MMA 2024</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MMA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Agricultura Sostenible</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CLP 500,000,000</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Programa para proyectos de agricultura sostenible y conservación ambiental</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Proyectos de agricultura sostenible</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://fondos.mma.gob.cl/agricultura-sostenible</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>agricultura@mma.gob.cl</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>Fondo Ambiental</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Agricultores, Organizaciones, Empresas</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>+56 2 2500 4000</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Teatinos 254, Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:18</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Activa Chile Apoya - CORFO</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CORFO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Desarrollo Rural</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Hasta 50,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Programa de cofinanciamiento para PYMES en recuperación económica. Apoyo para adquisición de activos fijos, infraestructura productiva y capital de trabajo.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Contribuyentes con inicio de actividades</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.corfo.cl/sites/cpp/programas_y_convocatorias/activa-chile-apoya</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>contacto@corfo.cl</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>Programa Público</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>PYMES con ventas entre 2.400 y 100.000 UF</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:39</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Consolida y Expande Innovación - CORFO</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CORFO</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Innovación Tecnológica</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Hasta 200,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Convocatoria para proyectos de innovación en etapa de expansión. Apoyo para consolidar y expandir iniciativas innovadoras.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Proyectos de innovación consolidados</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.corfo.cl/sites/cpp/programas_y_convocatorias/consolida-expande-innovacion</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>innovacion@corfo.cl</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>Convocatoria Innovación</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Empresas en etapa de expansión</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:39</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Innova Alta Tecnología - CORFO</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CORFO</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Innovación Tecnológica</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Hasta 500,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Convocatoria para proyectos de innovación tecnológica de alto impacto. Fomento a la innovación en tecnologías avanzadas.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Proyectos de innovación tecnológica</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.corfo.cl/sites/cpp/programas_y_convocatorias/innova-alta-tecnologia</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>tecnologia@corfo.cl</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>Convocatoria Tecnológica</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Empresas con proyectos de alta tecnología</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:39</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Crédito Siembra por Chile - BancoEstado</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BancoEstado</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Agricultura Sostenible</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Hasta 15,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Crédito destinado a financiar necesidades de capital de trabajo para establecimiento y producción de cultivos tradicionales.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Cultivos tradicionales (arroz, avena, cebada, etc.)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://www.bancoestado.cl/web/banco-estado/siembra-por-chile</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>agricultura@bancoestado.cl</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>Crédito Agrícola</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Agricultores y productores</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:40</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Crédito Mundo Verde - BancoEstado</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BancoEstado</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Agricultura Sostenible</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Hasta 25,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Crédito para financiar proyectos que promuevan energías limpias, eficiencia energética y fomento productivo sostenible.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Proyectos de eficiencia energética y sostenibilidad</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.bancoestado.cl/web/banco-estado/mundo-verde</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>verde@bancoestado.cl</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>Crédito Verde</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Empresas con certificaciones ambientales</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:40</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Concurso IDeA I+D Tecnologías Avanzadas 2025 - ANID</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ANID</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Innovación Tecnológica</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Hasta 80,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Convocatoria para proyectos de investigación y desarrollo en tecnologías avanzadas. Fomento a la I+D en tecnologías emergentes.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Proyectos de investigación en tecnologías avanzadas</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.anid.cl/concursos/idea-i-d-tecnologias-avanzadas-2025</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>idea@anid.cl</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>Convocatoria I+D</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Investigadores y centros de I+D</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:41</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FONDECYT Regular 2025 - ANID</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ANID</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Innovación Tecnológica</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hasta 60,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Fondo Nacional de Desarrollo Científico y Tecnológico para proyectos de investigación básica y aplicada.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Proyectos de investigación científica</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.anid.cl/concursos/fondecyt-regular-2025</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>fondecyt@anid.cl</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>Fondo de Investigación</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Investigadores con doctorado</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:41</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Crédito INDAP - Capital de Trabajo</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>INDAP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Desarrollo Rural</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Hasta 5,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Crédito a corto plazo con tasas subsidiadas para financiar capital de trabajo en actividades agrícolas.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Actividades agrícolas registradas</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.indap.gob.cl/creditos/capital-trabajo</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>creditos@indap.gob.cl</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Crédito Agrícola</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Pequeños agricultores</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:42</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Crédito INDAP - Inversión</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INDAP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Desarrollo Rural</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Hasta 15,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Crédito a mediano y largo plazo para inversión en infraestructura agrícola y equipamiento.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Proyectos de inversión agrícola</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.indap.gob.cl/creditos/inversion</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>inversion@indap.gob.cl</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Crédito de Inversión</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Pequeños y medianos agricultores</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:42</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Agroseguros - INDAP</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>INDAP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Agricultura Sostenible</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Hasta 20,000,000 CLP</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Seguros agrícolas con subsidios del Estado para proteger contra pérdidas por eventos climáticos.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Actividades agrícolas asegurables</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.indap.gob.cl/agroseguros</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>seguros@indap.gob.cl</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Seguro Agrícola</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Agricultores registrados</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:42</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fondo Verde del Clima - GCF</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GCF</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Agricultura Sostenible</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>USD 1,000,000 - 50,000,000</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Fondo internacional para financiar proyectos de adaptación y mitigación al cambio climático en países en desarrollo.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Proyectos de cambio climático</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.greenclimate.fund/funding/rfp-rfq</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>info@gcfund.org</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>Fondo Internacional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Gobiernos, ONGs, organizaciones internacionales</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:43</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Fondo de Adaptación - Adaptation Fund</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Adaptation Fund</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Agricultura Sostenible</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>USD 500,000 - 10,000,000</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Fondo internacional para financiar proyectos de adaptación al cambio climático en países en desarrollo.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Proyectos de adaptación climática</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.adaptation-fund.org/apply-for-funding/</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>info@adaptation-fund.org</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>Fondo de Adaptación</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Gobiernos, ONGs, organizaciones</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:43</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Programa de Desarrollo Rural - UE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unión Europea</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Desarrollo Rural</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EUR 100,000 - 2,000,000</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Programa de la Unión Europea para financiar proyectos de desarrollo rural y agricultura sostenible.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Proyectos de desarrollo rural</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://webgate.ec.europa.eu/europeaid/online-services</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>info@europa.eu</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>Programa UE</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Organizaciones de países elegibles</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:43</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Fondo de Innovación Agrícola - Gates Foundation</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Gates Foundation</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Innovación Tecnológica</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>USD 500,000 - 5,000,000</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Fondo para financiar innovaciones agrícolas que mejoren la productividad y sostenibilidad en países en desarrollo.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Proyectos de innovación agrícola</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://www.gatesfoundation.org/agricultural-innovation</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>agriculture@gatesfoundation.org</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>Fondo de Fundación</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Organizaciones de innovación agrícola</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:44</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Programa de Seguridad Alimentaria - Rockefeller Foundation</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Rockefeller Foundation</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Seguridad Alimentaria</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>USD 200,000 - 2,000,000</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Programa para financiar proyectos que mejoren la seguridad alimentaria y nutrición en comunidades vulnerables.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Proyectos de seguridad alimentaria</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://www.rockefellerfoundation.org/food-security/</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>food@rockefellerfoundation.org</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>Programa de Fundación</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Organizaciones de seguridad alimentaria</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>2026-04-06 10:55:44</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
